--- a/partial/sliding_window_results_window_9.xlsx
+++ b/partial/sliding_window_results_window_9.xlsx
@@ -463,13 +463,13 @@
         <v>29.81</v>
       </c>
       <c r="C2" t="n">
-        <v>30.38714239875284</v>
+        <v>30.16580649882934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5771423987528443</v>
+        <v>0.3558064988293452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3330933484381872</v>
+        <v>0.1265982646091968</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.92</v>
       </c>
       <c r="C3" t="n">
-        <v>30.20424264837479</v>
+        <v>29.91327755397509</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2842426483747857</v>
+        <v>-0.006722446024916451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08079388315511209</v>
+        <v>4.519128055791499e-05</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.98</v>
       </c>
       <c r="C4" t="n">
-        <v>29.60451508679434</v>
+        <v>29.92425137224613</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.375484913205657</v>
+        <v>-0.05574862775387501</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1409889200450598</v>
+        <v>0.003107909496440123</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.04</v>
       </c>
       <c r="C5" t="n">
-        <v>29.90138387639368</v>
+        <v>29.97212626215743</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1386161236063188</v>
+        <v>-0.06787373784256445</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01921442972364226</v>
+        <v>0.004606844288721166</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.21</v>
       </c>
       <c r="C6" t="n">
-        <v>29.52965659601929</v>
+        <v>30.00820204159942</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6803434039807073</v>
+        <v>-0.2017979584005793</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4628671473400559</v>
+        <v>0.04072241601464195</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.22</v>
       </c>
       <c r="C7" t="n">
-        <v>29.92241711051456</v>
+        <v>30.14504543960305</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2975828894854402</v>
+        <v>-0.0749545603969537</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08855557611450372</v>
+        <v>0.005618186124300579</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.38</v>
       </c>
       <c r="C8" t="n">
-        <v>29.82957776103391</v>
+        <v>30.20597661290189</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5504222389660889</v>
+        <v>-0.1740233870981065</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3029646411484422</v>
+        <v>0.03028413925709742</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.44</v>
       </c>
       <c r="C9" t="n">
-        <v>30.48748488097121</v>
+        <v>30.49339099702649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04748488097120784</v>
+        <v>0.05339099702649008</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002254813920849777</v>
+        <v>0.002850598563482673</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.48</v>
       </c>
       <c r="C10" t="n">
-        <v>30.35523971682203</v>
+        <v>30.50756586496083</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1247602831779666</v>
+        <v>0.02756586496083102</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01556512825864642</v>
+        <v>0.0007598769110387715</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.69</v>
       </c>
       <c r="C11" t="n">
-        <v>30.55629286458905</v>
+        <v>30.54467052631041</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1337071354109547</v>
+        <v>-0.1453294736895892</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01787759805980338</v>
+        <v>0.02112065592289299</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.75</v>
       </c>
       <c r="C12" t="n">
-        <v>30.34749455427049</v>
+        <v>30.73448260021426</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4025054457295099</v>
+        <v>-0.01551739978573963</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1620106338419114</v>
+        <v>0.0002407896961104722</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.94</v>
       </c>
       <c r="C13" t="n">
-        <v>30.63918103055309</v>
+        <v>30.86336916496587</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3008189694469117</v>
+        <v>-0.07663083503413404</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09049205237910198</v>
+        <v>0.005872284878028665</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.95</v>
       </c>
       <c r="C14" t="n">
-        <v>30.85205001054801</v>
+        <v>31.06634062460518</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09794998945199396</v>
+        <v>0.1163406246051828</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009594200433645728</v>
+        <v>0.01353514093352406</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.02</v>
       </c>
       <c r="C15" t="n">
-        <v>31.41783529191696</v>
+        <v>31.23863354218343</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3978352919169588</v>
+        <v>0.2186335421834329</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1582729194946518</v>
+        <v>0.04780062576767493</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.12</v>
       </c>
       <c r="C16" t="n">
-        <v>31.73871019207804</v>
+        <v>31.30623121835359</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6187101920780371</v>
+        <v>0.186231218353587</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3828023017812416</v>
+        <v>0.03468206668946141</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.28</v>
       </c>
       <c r="C17" t="n">
-        <v>31.81434325783658</v>
+        <v>31.14093985533413</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5343432578365821</v>
+        <v>-0.1390601446658728</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2855227171954121</v>
+        <v>0.01933772383449347</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.38</v>
       </c>
       <c r="C18" t="n">
-        <v>31.51369094615249</v>
+        <v>30.91667236706866</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1336909461524947</v>
+        <v>-0.4633276329313354</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01787326908314923</v>
+        <v>0.2146724954377543</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.58</v>
       </c>
       <c r="C19" t="n">
-        <v>31.87210189948917</v>
+        <v>31.11689710311405</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2921018994891682</v>
+        <v>-0.4631028968859496</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08532351968518012</v>
+        <v>0.2144642931041585</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.65</v>
       </c>
       <c r="C20" t="n">
-        <v>31.81605668925805</v>
+        <v>31.68030221163314</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1660566892580491</v>
+        <v>0.0303022116331455</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02757482404734427</v>
+        <v>0.0009182240298599387</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.88</v>
       </c>
       <c r="C21" t="n">
-        <v>32.49591812876506</v>
+        <v>32.55461467098568</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6159181287650632</v>
+        <v>0.6746146709856795</v>
       </c>
       <c r="E21" t="n">
-        <v>0.379355141341457</v>
+        <v>0.4551049543091166</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.28</v>
       </c>
       <c r="C22" t="n">
-        <v>32.39772312690157</v>
+        <v>32.5785735425166</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1177231269015735</v>
+        <v>0.2985735425165998</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01385873460748398</v>
+        <v>0.08914616029091185</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.45</v>
       </c>
       <c r="C23" t="n">
-        <v>32.47967215352129</v>
+        <v>32.77063300299165</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0296721535212825</v>
+        <v>0.3206330029916487</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0008804366945905572</v>
+        <v>0.1028055226074426</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.85</v>
       </c>
       <c r="C24" t="n">
-        <v>32.70930963669593</v>
+        <v>32.97614095206262</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.140690363304067</v>
+        <v>0.1261409520626202</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01979377832663037</v>
+        <v>0.01591153978726425</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.9</v>
       </c>
       <c r="C25" t="n">
-        <v>32.84341623544406</v>
+        <v>33.03574193207213</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.05658376455593839</v>
+        <v>0.1357419320721291</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00320172241132187</v>
+        <v>0.01842587212267452</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.1</v>
       </c>
       <c r="C26" t="n">
-        <v>33.22115909197819</v>
+        <v>33.25553034813504</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1211590919781855</v>
+        <v>0.1555303481350379</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01467952556897842</v>
+        <v>0.02418968919100607</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.4</v>
       </c>
       <c r="C27" t="n">
-        <v>33.7539685039599</v>
+        <v>33.5578811770355</v>
       </c>
       <c r="D27" t="n">
-        <v>0.353968503959905</v>
+        <v>0.157881177035506</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1252937017956133</v>
+        <v>0.02492646606211678</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.7</v>
       </c>
       <c r="C28" t="n">
-        <v>33.95208900788641</v>
+        <v>33.65613047871585</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2520890078864042</v>
+        <v>-0.04386952128415089</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06354886789715156</v>
+        <v>0.001924534897700568</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.1</v>
       </c>
       <c r="C29" t="n">
-        <v>34.04613279726959</v>
+        <v>33.75997469900986</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0538672027304159</v>
+        <v>-0.3400253009901419</v>
       </c>
       <c r="E29" t="n">
-        <v>0.002901675529999726</v>
+        <v>0.1156172053134366</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.4</v>
       </c>
       <c r="C30" t="n">
-        <v>34.35496298046779</v>
+        <v>34.34806229484705</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0450370195322094</v>
+        <v>-0.05193770515295171</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002028333128344611</v>
+        <v>0.002697525216554946</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.9</v>
       </c>
       <c r="C31" t="n">
-        <v>34.68193311658447</v>
+        <v>34.63708486459595</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2180668834155313</v>
+        <v>-0.2629151354040502</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04755316564256291</v>
+        <v>0.06912436842453006</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.3</v>
       </c>
       <c r="C32" t="n">
-        <v>35.42135877841788</v>
+        <v>35.70270976732756</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1213587784178856</v>
+        <v>0.4027097673275648</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01472795309908145</v>
+        <v>0.1621751567010214</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.7</v>
       </c>
       <c r="C33" t="n">
-        <v>35.84551657332369</v>
+        <v>35.96025172326057</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1455165733236825</v>
+        <v>0.2602517232605663</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02117507311186667</v>
+        <v>0.0677309594600944</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.3</v>
       </c>
       <c r="C34" t="n">
-        <v>36.0760419849652</v>
+        <v>36.3612699998228</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2239580150347962</v>
+        <v>0.06126999982279813</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05015719249832599</v>
+        <v>0.003754012878285683</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.8</v>
       </c>
       <c r="C35" t="n">
-        <v>37.00934890484561</v>
+        <v>36.87154410593212</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2093489048456121</v>
+        <v>0.07154410593212646</v>
       </c>
       <c r="E35" t="n">
-        <v>0.04382696396005714</v>
+        <v>0.005118559093627332</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.3</v>
       </c>
       <c r="C36" t="n">
-        <v>37.06469109587862</v>
+        <v>37.02772238973446</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2353089041213821</v>
+        <v>-0.2722776102655402</v>
       </c>
       <c r="E36" t="n">
-        <v>0.05537028035880577</v>
+        <v>0.0741350970519134</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.9</v>
       </c>
       <c r="C37" t="n">
-        <v>38.01732082355522</v>
+        <v>37.84576247163672</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1173208235552252</v>
+        <v>-0.05423752836328077</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01376417563967629</v>
+        <v>0.002941709482957686</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.5</v>
       </c>
       <c r="C38" t="n">
-        <v>38.66120263671617</v>
+        <v>38.55465602347439</v>
       </c>
       <c r="D38" t="n">
-        <v>0.161202636716169</v>
+        <v>0.05465602347438647</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02598629008424515</v>
+        <v>0.002987280902032685</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.9</v>
       </c>
       <c r="C39" t="n">
-        <v>39.08689015532173</v>
+        <v>39.13423377791571</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1868901553217341</v>
+        <v>0.234233777915712</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03492793015618191</v>
+        <v>0.05486546271666708</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.4</v>
       </c>
       <c r="C40" t="n">
-        <v>39.51705279847814</v>
+        <v>39.44887619032057</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1170527984781415</v>
+        <v>0.04887619032056989</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01370135763156441</v>
+        <v>0.00238888198025257</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.9</v>
       </c>
       <c r="C41" t="n">
-        <v>39.80047003346329</v>
+        <v>39.72291496082726</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.09952996653670709</v>
+        <v>-0.1770850391727379</v>
       </c>
       <c r="E41" t="n">
-        <v>0.009906214238798033</v>
+        <v>0.03135911109881011</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.1</v>
       </c>
       <c r="C42" t="n">
-        <v>39.94117075655549</v>
+        <v>39.76860165895368</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1588292434445151</v>
+        <v>-0.3313983410463237</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02522672857315704</v>
+        <v>0.1098248604482555</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.6</v>
       </c>
       <c r="C43" t="n">
-        <v>40.0960036439964</v>
+        <v>39.90242503756722</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5039963560035972</v>
+        <v>-0.6975749624327818</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2540123268649047</v>
+        <v>0.486610828213097</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.9</v>
       </c>
       <c r="C44" t="n">
-        <v>40.38686425707408</v>
+        <v>40.19112861176873</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5131357429259182</v>
+        <v>-0.7088713882312732</v>
       </c>
       <c r="E44" t="n">
-        <v>0.263308290668134</v>
+        <v>0.5024986450529324</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.2</v>
       </c>
       <c r="C45" t="n">
-        <v>41.23857153692916</v>
+        <v>41.19744794723858</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03857153692916171</v>
+        <v>-0.00255205276142334</v>
       </c>
       <c r="E45" t="n">
-        <v>0.001487763461077686</v>
+        <v>6.512973297088496e-06</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.5</v>
       </c>
       <c r="C46" t="n">
-        <v>41.47088209601379</v>
+        <v>41.2758958709417</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0291179039862115</v>
+        <v>-0.224104129058297</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0008478523325502317</v>
+        <v>0.05022266066097784</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.8</v>
       </c>
       <c r="C47" t="n">
-        <v>42.09844203448182</v>
+        <v>41.71022517673048</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2984420344818233</v>
+        <v>-0.08977482326951503</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08906764794564979</v>
+        <v>0.008059518893072656</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.2</v>
       </c>
       <c r="C48" t="n">
-        <v>42.39337219403187</v>
+        <v>42.38125921823084</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1933721940318662</v>
+        <v>0.1812592182308421</v>
       </c>
       <c r="E48" t="n">
-        <v>0.03739280542469772</v>
+        <v>0.03285490419365605</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.7</v>
       </c>
       <c r="C49" t="n">
-        <v>43.3717007085433</v>
+        <v>43.50843356850199</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6717007085432982</v>
+        <v>0.8084335685019894</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4511818418575689</v>
+        <v>0.6535648346808609</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>43.7</v>
       </c>
       <c r="C50" t="n">
-        <v>43.9667627965911</v>
+        <v>43.92855664015034</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2667627965910953</v>
+        <v>0.2285566401503374</v>
       </c>
       <c r="E50" t="n">
-        <v>0.07116238964510206</v>
+        <v>0.05223813775681082</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>44.2</v>
       </c>
       <c r="C51" t="n">
-        <v>43.48826428007315</v>
+        <v>44.19887121284617</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7117357199268568</v>
+        <v>-0.001128787153831468</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5065677350198011</v>
+        <v>1.274160438654945e-06</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.9776296810985414</v>
+        <v>0.06733617323221353</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.340535819661321</v>
+        <v>4.010449973461252</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1068107163932264</v>
+        <v>0.08020899946922504</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_9.xlsx
+++ b/partial/sliding_window_results_window_9.xlsx
@@ -463,13 +463,13 @@
         <v>29.81</v>
       </c>
       <c r="C2" t="n">
-        <v>30.16580649882934</v>
+        <v>29.85127023573228</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3558064988293452</v>
+        <v>0.04127023573228428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1265982646091968</v>
+        <v>0.001703232357398314</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.92</v>
       </c>
       <c r="C3" t="n">
-        <v>29.91327755397509</v>
+        <v>29.83342629791488</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006722446024916451</v>
+        <v>-0.0865737020851256</v>
       </c>
       <c r="E3" t="n">
-        <v>4.519128055791499e-05</v>
+        <v>0.007495005892724081</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.98</v>
       </c>
       <c r="C4" t="n">
-        <v>29.92425137224613</v>
+        <v>29.65040369417224</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05574862775387501</v>
+        <v>-0.3295963058277565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003107909496440123</v>
+        <v>0.108633724815304</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.04</v>
       </c>
       <c r="C5" t="n">
-        <v>29.97212626215743</v>
+        <v>29.89803689319474</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06787373784256445</v>
+        <v>-0.1419631068052567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004606844288721166</v>
+        <v>0.02015352369380072</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.21</v>
       </c>
       <c r="C6" t="n">
-        <v>30.00820204159942</v>
+        <v>29.90144356553505</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2017979584005793</v>
+        <v>-0.3085564344649541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04072241601464195</v>
+        <v>0.09520707324972549</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.22</v>
       </c>
       <c r="C7" t="n">
-        <v>30.14504543960305</v>
+        <v>30.11369658967995</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0749545603969537</v>
+        <v>-0.1063034103200451</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005618186124300579</v>
+        <v>0.01130041504567187</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.38</v>
       </c>
       <c r="C8" t="n">
-        <v>30.20597661290189</v>
+        <v>30.24836563430881</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1740233870981065</v>
+        <v>-0.1316343656911911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03028413925709742</v>
+        <v>0.01732760623092224</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.44</v>
       </c>
       <c r="C9" t="n">
-        <v>30.49339099702649</v>
+        <v>30.62523711997018</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05339099702649008</v>
+        <v>0.185237119970175</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002850598563482673</v>
+        <v>0.034312790614845</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.48</v>
       </c>
       <c r="C10" t="n">
-        <v>30.50756586496083</v>
+        <v>30.39808407575507</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02756586496083102</v>
+        <v>-0.08191592424493166</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0007598769110387715</v>
+        <v>0.006710218644901383</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.69</v>
       </c>
       <c r="C11" t="n">
-        <v>30.54467052631041</v>
+        <v>30.41921358062161</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1453294736895892</v>
+        <v>-0.2707864193783927</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02112065592289299</v>
+        <v>0.07332528491977074</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.75</v>
       </c>
       <c r="C12" t="n">
-        <v>30.73448260021426</v>
+        <v>30.6240693535542</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01551739978573963</v>
+        <v>-0.1259306464457985</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0002407896961104722</v>
+        <v>0.01585852771425671</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.94</v>
       </c>
       <c r="C13" t="n">
-        <v>30.86336916496587</v>
+        <v>30.60823660716525</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.07663083503413404</v>
+        <v>-0.3317633928347554</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005872284878028665</v>
+        <v>0.1100669488252282</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.95</v>
       </c>
       <c r="C14" t="n">
-        <v>31.06634062460518</v>
+        <v>30.6864300939923</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1163406246051828</v>
+        <v>-0.2635699060076995</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01353514093352406</v>
+        <v>0.06946909535290753</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.02</v>
       </c>
       <c r="C15" t="n">
-        <v>31.23863354218343</v>
+        <v>30.9805123971549</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2186335421834329</v>
+        <v>-0.039487602845103</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04780062576767493</v>
+        <v>0.001559270778452586</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.12</v>
       </c>
       <c r="C16" t="n">
-        <v>31.30623121835359</v>
+        <v>31.21532548179867</v>
       </c>
       <c r="D16" t="n">
-        <v>0.186231218353587</v>
+        <v>0.09532548179867106</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03468206668946141</v>
+        <v>0.009086947480148768</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.28</v>
       </c>
       <c r="C17" t="n">
-        <v>31.14093985533413</v>
+        <v>31.2909814677083</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1390601446658728</v>
+        <v>0.010981467708298</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01933772383449347</v>
+        <v>0.0001205926330283917</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.38</v>
       </c>
       <c r="C18" t="n">
-        <v>30.91667236706866</v>
+        <v>31.22626008027363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4633276329313354</v>
+        <v>-0.1537399197263731</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2146724954377543</v>
+        <v>0.02363596291747165</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.58</v>
       </c>
       <c r="C19" t="n">
-        <v>31.11689710311405</v>
+        <v>31.50998898293996</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4631028968859496</v>
+        <v>-0.07001101706003965</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2144642931041585</v>
+        <v>0.004901542509781163</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.65</v>
       </c>
       <c r="C20" t="n">
-        <v>31.68030221163314</v>
+        <v>31.53260303187228</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0303022116331455</v>
+        <v>-0.1173969681277143</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0009182240298599387</v>
+        <v>0.01378204812557956</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.88</v>
       </c>
       <c r="C21" t="n">
-        <v>32.55461467098568</v>
+        <v>32.12820877204209</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6746146709856795</v>
+        <v>0.2482087720420942</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4551049543091166</v>
+        <v>0.0616075945186443</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.28</v>
       </c>
       <c r="C22" t="n">
-        <v>32.5785735425166</v>
+        <v>32.00362661517347</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2985735425165998</v>
+        <v>-0.2763733848265346</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08914616029091185</v>
+        <v>0.0763822478404758</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.45</v>
       </c>
       <c r="C23" t="n">
-        <v>32.77063300299165</v>
+        <v>32.22458555325326</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3206330029916487</v>
+        <v>-0.2254144467467469</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1028055226074426</v>
+        <v>0.05081167280214201</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.85</v>
       </c>
       <c r="C24" t="n">
-        <v>32.97614095206262</v>
+        <v>32.939263189548</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1261409520626202</v>
+        <v>0.08926318954799939</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01591153978726425</v>
+        <v>0.007967917008282067</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.9</v>
       </c>
       <c r="C25" t="n">
-        <v>33.03574193207213</v>
+        <v>33.10000362862773</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1357419320721291</v>
+        <v>0.2000036286277265</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01842587212267452</v>
+        <v>0.04000145146425753</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.1</v>
       </c>
       <c r="C26" t="n">
-        <v>33.25553034813504</v>
+        <v>32.96533138526934</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1555303481350379</v>
+        <v>-0.1346686147306642</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02418968919100607</v>
+        <v>0.01813563579347606</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.4</v>
       </c>
       <c r="C27" t="n">
-        <v>33.5578811770355</v>
+        <v>33.55377770142751</v>
       </c>
       <c r="D27" t="n">
-        <v>0.157881177035506</v>
+        <v>0.1537777014275079</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02492646606211678</v>
+        <v>0.02364758145632777</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.7</v>
       </c>
       <c r="C28" t="n">
-        <v>33.65613047871585</v>
+        <v>33.44535829701062</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04386952128415089</v>
+        <v>-0.2546417029893817</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001924534897700568</v>
+        <v>0.06484239690133249</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.1</v>
       </c>
       <c r="C29" t="n">
-        <v>33.75997469900986</v>
+        <v>33.66950137641493</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3400253009901419</v>
+        <v>-0.4304986235850734</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1156172053134366</v>
+        <v>0.1853290649086427</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.4</v>
       </c>
       <c r="C30" t="n">
-        <v>34.34806229484705</v>
+        <v>34.10173157517261</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.05193770515295171</v>
+        <v>-0.2982684248273912</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002697525216554946</v>
+        <v>0.08896405324901314</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.9</v>
       </c>
       <c r="C31" t="n">
-        <v>34.63708486459595</v>
+        <v>34.70292423262139</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2629151354040502</v>
+        <v>-0.1970757673786068</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06912436842453006</v>
+        <v>0.03883885808786673</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.3</v>
       </c>
       <c r="C32" t="n">
-        <v>35.70270976732756</v>
+        <v>35.36107555239372</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4027097673275648</v>
+        <v>0.06107555239372431</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1621751567010214</v>
+        <v>0.003730223100198563</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.7</v>
       </c>
       <c r="C33" t="n">
-        <v>35.96025172326057</v>
+        <v>35.67484399564297</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2602517232605663</v>
+        <v>-0.02515600435703647</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0677309594600944</v>
+        <v>0.0006328245552112376</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.3</v>
       </c>
       <c r="C34" t="n">
-        <v>36.3612699998228</v>
+        <v>36.20749979100295</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06126999982279813</v>
+        <v>-0.09250020899704481</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003754012878285683</v>
+        <v>0.00855628866449697</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.8</v>
       </c>
       <c r="C35" t="n">
-        <v>36.87154410593212</v>
+        <v>36.82521361773482</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07154410593212646</v>
+        <v>0.02521361773482766</v>
       </c>
       <c r="E35" t="n">
-        <v>0.005118559093627332</v>
+        <v>0.0006357265192780162</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.3</v>
       </c>
       <c r="C36" t="n">
-        <v>37.02772238973446</v>
+        <v>36.98864591130644</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2722776102655402</v>
+        <v>-0.3113540886935553</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0741350970519134</v>
+        <v>0.0969413685461943</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.9</v>
       </c>
       <c r="C37" t="n">
-        <v>37.84576247163672</v>
+        <v>37.83608233489119</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.05423752836328077</v>
+        <v>-0.06391766510880359</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002941709482957686</v>
+        <v>0.004085467912961168</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.5</v>
       </c>
       <c r="C38" t="n">
-        <v>38.55465602347439</v>
+        <v>38.53709879342688</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05465602347438647</v>
+        <v>0.03709879342687827</v>
       </c>
       <c r="E38" t="n">
-        <v>0.002987280902032685</v>
+        <v>0.001376320473730187</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.9</v>
       </c>
       <c r="C39" t="n">
-        <v>39.13423377791571</v>
+        <v>38.87974051938805</v>
       </c>
       <c r="D39" t="n">
-        <v>0.234233777915712</v>
+        <v>-0.02025948061194782</v>
       </c>
       <c r="E39" t="n">
-        <v>0.05486546271666708</v>
+        <v>0.0004104465546658897</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.4</v>
       </c>
       <c r="C40" t="n">
-        <v>39.44887619032057</v>
+        <v>39.23119207011828</v>
       </c>
       <c r="D40" t="n">
-        <v>0.04887619032056989</v>
+        <v>-0.1688079298817229</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00238888198025257</v>
+        <v>0.02849611719095267</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.9</v>
       </c>
       <c r="C41" t="n">
-        <v>39.72291496082726</v>
+        <v>39.6817795122272</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1770850391727379</v>
+        <v>-0.2182204877727969</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03135911109881011</v>
+        <v>0.0476201812837974</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.1</v>
       </c>
       <c r="C42" t="n">
-        <v>39.76860165895368</v>
+        <v>39.59428813193553</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3313983410463237</v>
+        <v>-0.5057118680644734</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1098248604482555</v>
+        <v>0.2557444935012594</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.6</v>
       </c>
       <c r="C43" t="n">
-        <v>39.90242503756722</v>
+        <v>39.73246893358794</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.6975749624327818</v>
+        <v>-0.867531066412063</v>
       </c>
       <c r="E43" t="n">
-        <v>0.486610828213097</v>
+        <v>0.7526101511900513</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.9</v>
       </c>
       <c r="C44" t="n">
-        <v>40.19112861176873</v>
+        <v>40.02412746273924</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7088713882312732</v>
+        <v>-0.8758725372607614</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5024986450529324</v>
+        <v>0.767152701527604</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.2</v>
       </c>
       <c r="C45" t="n">
-        <v>41.19744794723858</v>
+        <v>41.31088184984706</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.00255205276142334</v>
+        <v>0.1108818498470541</v>
       </c>
       <c r="E45" t="n">
-        <v>6.512973297088496e-06</v>
+        <v>0.01229478462550464</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.5</v>
       </c>
       <c r="C46" t="n">
-        <v>41.2758958709417</v>
+        <v>41.21777120880313</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.224104129058297</v>
+        <v>-0.2822287911968715</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05022266066097784</v>
+        <v>0.0796530905804473</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.8</v>
       </c>
       <c r="C47" t="n">
-        <v>41.71022517673048</v>
+        <v>41.47481210548713</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.08977482326951503</v>
+        <v>-0.3251878945128652</v>
       </c>
       <c r="E47" t="n">
-        <v>0.008059518893072656</v>
+        <v>0.1057471667377104</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.2</v>
       </c>
       <c r="C48" t="n">
-        <v>42.38125921823084</v>
+        <v>42.34649467452427</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1812592182308421</v>
+        <v>0.1464946745242628</v>
       </c>
       <c r="E48" t="n">
-        <v>0.03285490419365605</v>
+        <v>0.02146068966396969</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.7</v>
       </c>
       <c r="C49" t="n">
-        <v>43.50843356850199</v>
+        <v>43.56827336457731</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8084335685019894</v>
+        <v>0.8682733645773055</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6535648346808609</v>
+        <v>0.7538986356343945</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>43.7</v>
       </c>
       <c r="C50" t="n">
-        <v>43.92855664015034</v>
+        <v>43.86916639894137</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2285566401503374</v>
+        <v>0.1691663989413712</v>
       </c>
       <c r="E50" t="n">
-        <v>0.05223813775681082</v>
+        <v>0.02861727053079115</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>44.2</v>
       </c>
       <c r="C51" t="n">
-        <v>44.19887121284617</v>
+        <v>43.69943391633888</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.001128787153831468</v>
+        <v>-0.500566083661127</v>
       </c>
       <c r="E51" t="n">
-        <v>1.274160438654945e-06</v>
+        <v>0.2505664041118384</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.06733617323221353</v>
+        <v>-6.191212345180425</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4.010449973461252</v>
+        <v>4.501408638737436</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.08020899946922504</v>
+        <v>0.09002817277474871</v>
       </c>
     </row>
   </sheetData>
